--- a/Luban/Config/Datas/Levels/L25/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L25/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L25 W1/25; N=55; EHP=360.580000; normal:17x27,normal:18x28</t>
+          <t>L25 W1/25; N=55; EHP=979.020526; normal:17x27,normal:18x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L25 W2/25; N=61; EHP=418.752044; normal:17x31,normal:18x30</t>
+          <t>L25 W2/25; N=61; EHP=1136.965018; normal:17x31,normal:18x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10020032,10020034,10048914,10020032,10020034,10048914,10020032,10020034,10048915,10020032,10020034,10048916,10020032,10020034,10048916,10020032,10020034,10048917,10020032,10020034,10048917,10020032,10020034,10048918,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020032,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033</t>
+          <t>10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020034,10020032,10020032,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033,10020033</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L25 W3/25; N=67; EHP=508.829517; air:2x2,air:11x1,air:12x2,air:13x2,air:14x1,normal:17x20,normal:18x21,swarm:84x18</t>
+          <t>L25 W3/25; N=67; EHP=1489.507711; normal:17x20,normal:18x29,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10020035,10020037,10048919,10020035,10020037,10048919,10020035,10020037,10048920,10020035,10020037,10048920,10020035,10020037,10048921,10020035,10020037,10048922,10020035,10020037,10048922,10020035,10020037,10048923,10020035,10020037,10048923,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020035,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036</t>
+          <t>10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020037,10020035,10020035,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020036,10020035,10020035,10020035,10020035,10020035,10020035,10020035,10020035,10020035</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L25 W4/25; N=73; EHP=638.388533; air:2x2,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x22,normal:18x22,swarm:84x20</t>
+          <t>L25 W4/25; N=73; EHP=1873.844325; normal:17x31,normal:18x22,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10020038,10020041,10048924,10020040,10020038,10020041,10048925,10020040,10020038,10020041,10048925,10020040,10020038,10020041,10048926,10020040,10020038,10020041,10048926,10020042,10020038,10020041,10048927,10020042,10020038,10020041,10048927,10020042,10020038,10020041,10048928,10020043,10020038,10020041,10048928,10020043,10020038,10020041,10020043,10020038,10020041,10020043,10020038,10020041,10020038,10020041,10020038,10020041,10020038,10020041,10020038,10020041,10020038,10020041,10020038,10020041,10020039,10020041,10020039,10020041,10020039,10020041,10020039,10020041,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039</t>
+          <t>10020038,10048924,10048924,10020040,10020038,10048925,10048925,10020040,10020038,10048925,10048925,10020040,10020038,10048926,10048926,10020040,10020038,10048926,10048926,10020042,10020038,10048927,10048927,10020042,10020038,10048927,10048927,10020042,10020038,10048928,10048928,10020043,10020038,10048928,10048928,10020043,10020038,10020041,10020043,10020038,10020041,10020043,10020038,10020041,10020038,10020041,10020038,10020041,10020038,10020041,10020038,10020041,10020038,10020041,10020038,10020041,10020039,10020041,10020039,10020041,10020039,10020041,10020039,10020041,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039,10020039</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L25 W5/25; N=79; EHP=1192.000000; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x19,medium:83x4,swarm:84x22,medium:108x3,medium:123x4</t>
+          <t>L25 W5/25; N=79; EHP=3275.766919; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x3,medium:123x4,normal:17x18,normal:18x19,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10020047,10020053,10020049,10048929,10020052,10020047,10020053,10020049,10048929,10020052,10020047,10020053,10020049,10020044,10020052,10020047,10020053,10020050,10020044,10020052,10020047,10020053,10020050,10048930,10020055,10020047,10020053,10020051,10048930,10020055,10020047,10020053,10020051,10020045,10020055,10020047,10020053,10020051,10020045,10020055,10020047,10020053,10020054,10020046,10020056,10020047,10020053,10020054,10020046,10020056,10020047,10020053,10020056,10020047,10020053,10020056,10020047,10020053,10020047,10020053,10020047,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020048,10020048,10020048,10020048,10020048,10020048</t>
+          <t>10020047,10048929,10020049,10048929,10020052,10020047,10048929,10020049,10048929,10020052,10020047,10020044,10020049,10020044,10020052,10020047,10020044,10020050,10020044,10020052,10020047,10048930,10020050,10048930,10020055,10020047,10048930,10020051,10048930,10020055,10020047,10020045,10020051,10020045,10020055,10020047,10020045,10020051,10020045,10020055,10020047,10020046,10020054,10020046,10020056,10020047,10020046,10020054,10020046,10020056,10020047,10020053,10020056,10020047,10020053,10020056,10020047,10020053,10020047,10020053,10020047,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020053,10020048,10020048,10020048,10020048,10020048,10020048,10020048</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L25 W6/25; N=85; EHP=1216.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x3,fast:58x2,fast:64x3,medium:83x4,swarm:84x23,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L25 W6/25; N=85; EHP=3343.733592; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10020060,10020066,10020062,10048931,10020065,10020060,10020066,10020062,10048931,10020065,10020060,10020066,10020062,10020057,10020065,10020060,10020066,10020063,10020057,10020065,10020060,10020066,10020063,10048932,10020068,10020060,10020066,10020064,10048932,10020068,10020060,10020066,10020064,10020058,10020068,10020060,10020066,10020067,10020058,10020068,10020060,10020066,10020067,10020059,10020068,10020060,10020066,10020067,10020059,10020069,10020060,10020066,10020059,10020069,10020060,10020066,10020069,10020060,10020066,10020069,10020060,10020066,10020060,10020066,10020060,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020061,10020061,10020061,10020061,10020061,10020061</t>
+          <t>10020060,10048931,10020062,10048931,10020065,10020060,10048931,10020062,10048931,10020065,10020060,10020057,10020062,10020057,10020065,10020060,10020057,10020063,10020057,10020065,10020060,10048932,10020063,10048932,10020068,10020060,10048932,10020064,10048932,10020068,10020060,10020058,10020064,10020058,10020068,10020060,10020058,10020067,10020058,10020068,10020060,10020059,10020067,10020059,10020068,10020060,10020059,10020067,10020059,10020069,10020060,10020059,10020059,10020069,10020060,10020066,10020069,10020060,10020066,10020069,10020060,10020066,10020060,10020066,10020060,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020066,10020061,10020061,10020061,10020061,10020061,10020061,10020061</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L25 W7/25; N=91; EHP=1364.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x3,normal:17x16,normal:18x16,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x25,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L25 W7/25; N=91; EHP=3752.046439; air:2x4,air:11x4,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x5,medium:123x4,normal:17x16,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10020073,10020079,10020075,10048933,10020078,10020073,10020079,10020075,10048933,10020078,10020073,10020079,10020076,10048933,10020078,10020073,10020079,10020076,10020070,10020078,10020073,10020079,10020076,10020070,10020078,10020073,10020079,10020077,10048934,10020081,10020073,10020079,10020077,10048934,10020081,10020073,10020079,10020077,10048934,10020081,10020073,10020079,10020080,10020071,10020081,10020073,10020079,10020080,10020071,10020082,10020073,10020079,10020080,10020072,10020082,10020073,10020079,10020072,10020082,10020073,10020079,10020082,10020073,10020079,10020082,10020073,10020079,10020073,10020079,10020073,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020074,10020074,10020074,10020074,10020074</t>
+          <t>10020073,10048933,10020075,10048933,10020078,10020073,10048933,10020075,10048933,10020078,10020073,10048933,10020076,10048933,10020078,10020073,10020070,10020076,10020070,10020078,10020073,10020070,10020076,10020070,10020078,10020073,10048934,10020077,10048934,10020081,10020073,10048934,10020077,10048934,10020081,10020073,10048934,10020077,10048934,10020081,10020073,10020071,10020080,10020071,10020081,10020073,10020071,10020080,10020071,10020082,10020073,10020072,10020080,10020072,10020082,10020073,10020072,10020072,10020082,10020073,10020079,10020082,10020073,10020079,10020082,10020073,10020079,10020073,10020079,10020073,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020079,10020074,10020074,10020074,10020074,10020074,10020074</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L25 W8/25; N=97; EHP=1752.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x17,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x5,swarm:84x27,fast:98x3,medium:108x4,medium:123x5</t>
+          <t>L25 W8/25; N=97; EHP=4820.968693; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x4,medium:123x5,normal:17x17,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10020086,10020092,10020088,10048935,10020091,10020086,10020092,10020088,10048935,10020091,10020086,10020092,10020088,10048935,10020091,10020086,10020092,10020089,10020083,10020091,10020086,10020092,10020089,10020083,10020091,10020086,10020092,10020089,10048936,10020094,10020086,10020092,10020090,10048936,10020094,10020086,10020092,10020090,10020084,10020094,10020086,10020092,10020090,10020084,10020094,10020086,10020092,10020093,10020084,10020094,10020086,10020092,10020093,10020085,10020095,10020086,10020092,10020093,10020085,10020095,10020086,10020092,10020095,10020086,10020092,10020095,10020086,10020092,10020095,10020086,10020092,10020086,10020092,10020086,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020087,10020087,10020087,10020087,10020087,10020087,10020087</t>
+          <t>10020086,10048935,10020088,10048935,10020091,10020086,10048935,10020088,10048935,10020091,10020086,10048935,10020088,10048935,10020091,10020086,10020083,10020089,10020083,10020091,10020086,10020083,10020089,10020083,10020091,10020086,10048936,10020089,10048936,10020094,10020086,10048936,10020090,10048936,10020094,10020086,10020084,10020090,10020084,10020094,10020086,10020084,10020090,10020084,10020094,10020086,10020084,10020093,10020084,10020094,10020086,10020085,10020093,10020085,10020095,10020086,10020085,10020093,10020085,10020095,10020086,10020092,10020095,10020086,10020092,10020095,10020086,10020092,10020095,10020086,10020092,10020086,10020092,10020086,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020092,10020087,10020087,10020087,10020087,10020087,10020087,10020087,10020087</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L25 W9/25; N=103; EHP=2235.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x18,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L25 W9/25; N=103; EHP=6144.720075; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x18,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10020099,10020105,10020101,10048937,10020104,10020099,10020105,10020101,10048937,10020104,10020099,10020105,10020101,10020096,10020104,10020099,10020105,10020102,10020096,10020104,10020099,10020105,10020102,10020096,10020104,10020099,10020105,10020102,10048938,10020107,10020099,10020105,10020103,10048938,10020107,10020099,10020105,10020103,10020097,10020107,10020099,10020105,10020103,10020097,10020107,10020099,10020105,10020103,10020097,10020107,10020099,10020105,10020106,10020098,10020107,10020099,10020105,10020106,10020098,10020108,10020099,10020105,10020106,10020098,10020108,10020099,10020105,10020108,10020099,10020105,10020108,10020099,10020105,10020108,10020099,10020105,10020099,10020105,10020099,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020100,10020100,10020100,10020100,10020100,10020100</t>
+          <t>10020099,10048937,10020101,10048937,10020104,10020099,10048937,10020101,10048937,10020104,10020099,10020096,10020101,10020096,10020104,10020099,10020096,10020102,10020096,10020104,10020099,10020096,10020102,10020096,10020104,10020099,10048938,10020102,10048938,10020107,10020099,10048938,10020103,10048938,10020107,10020099,10020097,10020103,10020097,10020107,10020099,10020097,10020103,10020097,10020107,10020099,10020097,10020103,10020097,10020107,10020099,10020098,10020106,10020098,10020107,10020099,10020098,10020106,10020098,10020108,10020099,10020098,10020106,10020098,10020108,10020099,10020105,10020108,10020099,10020105,10020108,10020099,10020105,10020108,10020099,10020105,10020099,10020105,10020099,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020105,10020100,10020100,10020100,10020100,10020100,10020100,10020100</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L25 W10/25; N=109; EHP=4119.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x19,normal:18x18,fast:30x3,fast:58x3,fast:64x4,medium:83x5,swarm:84x30,fast:98x3,medium:108x6,medium:123x5</t>
+          <t>L25 W10/25; N=109; EHP=11328.128279; air:2x4,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x4,fast:98x3,medium:83x5,medium:108x6,medium:123x5,normal:17x19,normal:18x18,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10020109,10020119,10020111,10048939,10020118,10045270,10020109,10020119,10020111,10048939,10020118,10020112,10020109,10020119,10020111,10048939,10020118,10020112,10020109,10020119,10020111,10048940,10020118,10020115,10020109,10020119,10020113,10048940,10020118,10020116,10020109,10020119,10020113,10048940,10020118,10020116,10020109,10020119,10020113,10048941,10020122,10020117,10020109,10020119,10020114,10048941,10020122,10045271,10020109,10020119,10020114,10048941,10020122,10020120,10020109,10020119,10020114,10048942,10020122,10020124,10020109,10020119,10020121,10048942,10020122,10020124,10020109,10020119,10020121,10048943,10020123,10020109,10020119,10020121,10048943,10020123,10020109,10020119,10048943,10020123,10020110,10020119,10020123,10020110,10020119,10020123,10020110,10020119,10020123,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020119,10020119,10020119,10020119</t>
+          <t>10020109,10048939,10020111,10048939,10020118,10045270,10020109,10048939,10020111,10048939,10020118,10020112,10020109,10048939,10020111,10048939,10020118,10020112,10020109,10048940,10020111,10048940,10020118,10020115,10020109,10048940,10020113,10048940,10020118,10020116,10020109,10048940,10020113,10048940,10020118,10020116,10020109,10048941,10020113,10048941,10020122,10020117,10020109,10048941,10020114,10048941,10020122,10045271,10020109,10048941,10020114,10048941,10020122,10020120,10020109,10048942,10020114,10048942,10020122,10020124,10020109,10048942,10020121,10048942,10020122,10020124,10020109,10048943,10020121,10048943,10020123,10020109,10048943,10020121,10048943,10020123,10020109,10048943,10048943,10020123,10020110,10020119,10020123,10020110,10020119,10020123,10020110,10020119,10020123,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020110,10020119,10020119,10020119,10020119,10020119</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L25 W11/25; N=115; EHP=4202.000000; air:2x3,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x14,fast:30x4,heavy:31x1,heavy:40x2,fast:58x3,fast:64x3,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x32,heavy:86x1,heavy:88x1,fast:98x3,medium:108x5,medium:123x6,heavy:127x2</t>
+          <t>L25 W11/25; N=115; EHP=11542.905752; air:2x6,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x5,medium:123x6,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10020128,10020137,10020130,10048944,10020136,10045272,10020128,10020137,10020130,10048944,10020136,10045273,10020128,10020137,10020130,10048944,10020136,10020133,10020128,10020137,10020131,10020125,10020136,10020133,10020128,10020137,10020131,10020125,10020136,10020134,10020128,10020137,10020131,10020125,10020136,10020134,10020128,10020137,10020131,10048945,10020141,10020135,10020128,10020137,10020132,10048945,10020141,10020138,10020128,10020137,10020132,10048945,10020141,10020139,10020128,10020137,10020132,10020126,10020141,10020139,10020128,10020137,10020140,10020126,10020141,10020143,10020128,10020137,10020140,10020126,10020141,10020143,10020128,10020137,10020140,10020127,10020142,10020128,10020137,10020140,10020127,10020142,10020128,10020137,10020127,10020142,10020129,10020137,10020142,10020129,10020137,10020142,10020129,10020137,10020142,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020137,10020137,10020137,10020137</t>
+          <t>10020128,10048944,10020130,10048944,10020136,10045272,10020128,10048944,10020130,10048944,10020136,10045273,10020128,10048944,10020130,10048944,10020136,10020133,10020128,10020125,10020131,10020125,10020136,10020133,10020128,10020125,10020131,10020125,10020136,10020134,10020128,10020125,10020131,10020125,10020136,10020134,10020128,10048945,10020131,10048945,10020141,10020135,10020128,10048945,10020132,10048945,10020141,10020138,10020128,10048945,10020132,10048945,10020141,10020139,10020128,10020126,10020132,10020126,10020141,10020139,10020128,10020126,10020140,10020126,10020141,10020143,10020128,10020126,10020140,10020126,10020141,10020143,10020128,10020127,10020140,10020127,10020142,10020128,10020127,10020140,10020127,10020142,10020128,10020127,10020127,10020142,10020129,10020137,10020142,10020129,10020137,10020142,10020129,10020137,10020142,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020129,10020137,10020137,10020137,10020137,10020137</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L25 W12/25; N=121; EHP=4348.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x14,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x33,heavy:86x1,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L25 W12/25; N=121; EHP=11945.801290; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10020147,10020157,10020149,10048946,10020156,10020150,10020147,10020157,10020149,10048946,10020156,10045274,10020147,10020157,10020149,10048946,10020156,10020153,10020147,10020157,10020149,10020144,10020156,10020153,10020147,10020157,10020151,10020144,10020156,10020154,10020147,10020157,10020151,10020144,10020156,10020154,10020147,10020157,10020151,10048947,10020161,10020155,10020147,10020157,10020151,10048947,10020161,10020155,10020147,10020157,10020152,10048947,10020161,10020158,10020147,10020157,10020152,10020145,10020161,10020159,10020147,10020157,10020152,10020145,10020161,10020159,10020147,10020157,10020152,10020145,10020161,10045275,10020147,10020157,10020160,10020146,10020161,10020147,10020157,10020160,10020146,10020162,10020147,10020157,10020160,10020146,10020162,10020148,10020157,10020162,10020148,10020157,10020162,10020148,10020157,10020162,10020148,10020157,10020162,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020157,10020157,10020157,10020157</t>
+          <t>10020147,10048946,10020149,10048946,10020156,10020150,10020147,10048946,10020149,10048946,10020156,10045274,10020147,10048946,10020149,10048946,10020156,10020153,10020147,10020144,10020149,10020144,10020156,10020153,10020147,10020144,10020151,10020144,10020156,10020154,10020147,10020144,10020151,10020144,10020156,10020154,10020147,10048947,10020151,10048947,10020161,10020155,10020147,10048947,10020151,10048947,10020161,10020155,10020147,10048947,10020152,10048947,10020161,10020158,10020147,10020145,10020152,10020145,10020161,10020159,10020147,10020145,10020152,10020145,10020161,10020159,10020147,10020145,10020152,10020145,10020161,10045275,10020147,10020146,10020160,10020146,10020161,10020147,10020146,10020160,10020146,10020162,10020147,10020146,10020160,10020146,10020162,10020148,10020157,10020162,10020148,10020157,10020162,10020148,10020157,10020162,10020148,10020157,10020162,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020148,10020157,10020157,10020157,10020157,10020157</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L25 W13/25; N=127; EHP=5302.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x35,heavy:86x1,heavy:88x2,fast:98x3,medium:108x7,medium:123x6,heavy:127x1</t>
+          <t>L25 W13/25; N=127; EHP=14559.252232; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x6,medium:108x7,medium:123x6,normal:17x15,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10020166,10020176,10020168,10048948,10020175,10020169,10020166,10020176,10020168,10048948,10020175,10020169,10020166,10020176,10020168,10048948,10020175,10020170,10020166,10020176,10020168,10048948,10020175,10020173,10020166,10020176,10020171,10020163,10020175,10020173,10020166,10020176,10020171,10020163,10020175,10045276,10020166,10020176,10020171,10020163,10020175,10020174,10020166,10020176,10020172,10048949,10020180,10020174,10020166,10020176,10020172,10048949,10020180,10020177,10020166,10020176,10020172,10048949,10020180,10020177,10020166,10020176,10020172,10020164,10020180,10020178,10020166,10020176,10020179,10020164,10020180,10020178,10020166,10020176,10020179,10020164,10020180,10045277,10020166,10020176,10020179,10020165,10020181,10020166,10020176,10020179,10020165,10020181,10020166,10020176,10020165,10020181,10020166,10020176,10020181,10020167,10020176,10020181,10020167,10020176,10020181,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020176,10020176,10020176,10020176</t>
+          <t>10020166,10048948,10020168,10048948,10020175,10020169,10020166,10048948,10020168,10048948,10020175,10020169,10020166,10048948,10020168,10048948,10020175,10020170,10020166,10048948,10020168,10048948,10020175,10020173,10020166,10020163,10020171,10020163,10020175,10020173,10020166,10020163,10020171,10020163,10020175,10045276,10020166,10020163,10020171,10020163,10020175,10020174,10020166,10048949,10020172,10048949,10020180,10020174,10020166,10048949,10020172,10048949,10020180,10020177,10020166,10048949,10020172,10048949,10020180,10020177,10020166,10020164,10020172,10020164,10020180,10020178,10020166,10020164,10020179,10020164,10020180,10020178,10020166,10020164,10020179,10020164,10020180,10045277,10020166,10020165,10020179,10020165,10020181,10020166,10020165,10020179,10020165,10020181,10020166,10020165,10020165,10020181,10020166,10020176,10020181,10020167,10020176,10020181,10020167,10020176,10020181,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020167,10020176,10020176,10020176,10020176,10020176</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L25 W14/25; N=133; EHP=6396.000000; air:2x4,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x17,normal:18x16,fast:30x4,heavy:31x2,heavy:40x1,fast:58x3,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x37,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L25 W14/25; N=133; EHP=17567.443262; air:2x8,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x6,medium:123x6,normal:17x17,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10020185,10020196,10020187,10048950,10020195,10020188,10020192,10020185,10020196,10020187,10048950,10020195,10020188,10020185,10020196,10020187,10048950,10020195,10020189,10020185,10020196,10020187,10020182,10020195,10020189,10020185,10020196,10020190,10020182,10020195,10045278,10020185,10020196,10020190,10020182,10020195,10020193,10020185,10020196,10020190,10020182,10020200,10020194,10020185,10020196,10020190,10048951,10020200,10020194,10020185,10020196,10020191,10048951,10020200,10020197,10020185,10020196,10020191,10048951,10020200,10020197,10020185,10020196,10020191,10020183,10020200,10020198,10020185,10020196,10020191,10020183,10020200,10020198,10020185,10020196,10020199,10020183,10020200,10020202,10020185,10020196,10020199,10020183,10020201,10020185,10020196,10020199,10020184,10020201,10020185,10020196,10020199,10020184,10020201,10020185,10020196,10020184,10020201,10020186,10020196,10020201,10020186,10020196,10020201,10020186,10020196,10020201,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020196,10020196,10020196,10020196</t>
+          <t>10020185,10048950,10020187,10048950,10020195,10020188,10020192,10020185,10048950,10020187,10048950,10020195,10020188,10020185,10048950,10020187,10048950,10020195,10020189,10020185,10020182,10020187,10020182,10020195,10020189,10020185,10020182,10020190,10020182,10020195,10045278,10020185,10020182,10020190,10020182,10020195,10020193,10020185,10020182,10020190,10020182,10020200,10020194,10020185,10048951,10020190,10048951,10020200,10020194,10020185,10048951,10020191,10048951,10020200,10020197,10020185,10048951,10020191,10048951,10020200,10020197,10020185,10020183,10020191,10020183,10020200,10020198,10020185,10020183,10020191,10020183,10020200,10020198,10020185,10020183,10020199,10020183,10020200,10020202,10020185,10020183,10020199,10020183,10020201,10020185,10020184,10020199,10020184,10020201,10020185,10020184,10020199,10020184,10020201,10020185,10020184,10020184,10020201,10020186,10020196,10020201,10020186,10020196,10020201,10020186,10020196,10020201,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020186,10020196,10020196,10020196,10020196,10020196</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L25 W15/25; N=139; EHP=11162.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x38,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L25 W15/25; N=139; EHP=30655.896520; air:2x6,air:11x8,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10020203,10020214,10020205,10048952,10020213,10020206,10020203,10020214,10020205,10048952,10020213,10020206,10020203,10020214,10020205,10048952,10020213,10020207,10020203,10020214,10020205,10048953,10020213,10020207,10020203,10020214,10020208,10048953,10020213,10020210,10020203,10020214,10020208,10048953,10020213,10020211,10020203,10020214,10020208,10048953,10020213,10020211,10020203,10020214,10020208,10048954,10020217,10020212,10020203,10020214,10020209,10048954,10020217,10020212,10020203,10020214,10020209,10048954,10020217,10020215,10020203,10020214,10020209,10048955,10020217,10020215,10020203,10020214,10020209,10048955,10020217,10045279,10020203,10020214,10020216,10048955,10020217,10020219,10020203,10020214,10020216,10048956,10020217,10020219,10020203,10020214,10020216,10048956,10020218,10020203,10020214,10020216,10048956,10020218,10020203,10020214,10020216,10048956,10020218,10020203,10020214,10020218,10020204,10020214,10020218,10020204,10020214,10020218,10020204,10020214,10020218,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020214,10020214,10020214,10020214</t>
+          <t>10020203,10048952,10020205,10048952,10020213,10020206,10020203,10048952,10020205,10048952,10020213,10020206,10020203,10048952,10020205,10048952,10020213,10020207,10020203,10048953,10020205,10048953,10020213,10020207,10020203,10048953,10020208,10048953,10020213,10020210,10020203,10048953,10020208,10048953,10020213,10020211,10020203,10048953,10020208,10048953,10020213,10020211,10020203,10048954,10020208,10048954,10020217,10020212,10020203,10048954,10020209,10048954,10020217,10020212,10020203,10048954,10020209,10048954,10020217,10020215,10020203,10048955,10020209,10048955,10020217,10020215,10020203,10048955,10020209,10048955,10020217,10045279,10020203,10048955,10020216,10048955,10020217,10020219,10020203,10048956,10020216,10048956,10020217,10020219,10020203,10048956,10020216,10048956,10020218,10020203,10048956,10020216,10048956,10020218,10020203,10048956,10020216,10048956,10020218,10020203,10020214,10020218,10020204,10020214,10020218,10020204,10020214,10020218,10020204,10020214,10020218,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020204,10020214,10020214,10020214,10020214,10020214</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L25 W16/25; N=145; EHP=11386.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x4,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x1,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L25 W16/25; N=145; EHP=31263.404807; air:2x6,air:11x8,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10020223,10020233,10020225,10048957,10020232,10020226,10020223,10020233,10020225,10048957,10020232,10020226,10020223,10020233,10020225,10048957,10020232,10020227,10020223,10020233,10020225,10048957,10020232,10020227,10020223,10020233,10020228,10020220,10020232,10020230,10020223,10020233,10020228,10020220,10020232,10020230,10020223,10020233,10020228,10020220,10020232,10020231,10020223,10020233,10020228,10048958,10020232,10020231,10020223,10020233,10020228,10048958,10020237,10045280,10020223,10020233,10020229,10048958,10020237,10020234,10020223,10020233,10020229,10048958,10020237,10020234,10020223,10020233,10020229,10020221,10020237,10020235,10020223,10020233,10020229,10020221,10020237,10020235,10020223,10020233,10020229,10020221,10020237,10020239,10020223,10020233,10020236,10020222,10020237,10020239,10020223,10020233,10020236,10020222,10020238,10020223,10020233,10020236,10020222,10020238,10020223,10020233,10020236,10020222,10020238,10020224,10020233,10020238,10020224,10020233,10020238,10020224,10020233,10020238,10020224,10020233,10020238,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020233,10020233,10020233,10020233,10020233,10020233</t>
+          <t>10020223,10048957,10020225,10048957,10020232,10020226,10020223,10048957,10020225,10048957,10020232,10020226,10020223,10048957,10020225,10048957,10020232,10020227,10020223,10048957,10020225,10048957,10020232,10020227,10020223,10020220,10020228,10020220,10020232,10020230,10020223,10020220,10020228,10020220,10020232,10020230,10020223,10020220,10020228,10020220,10020232,10020231,10020223,10048958,10020228,10048958,10020232,10020231,10020223,10048958,10020228,10048958,10020237,10045280,10020223,10048958,10020229,10048958,10020237,10020234,10020223,10048958,10020229,10048958,10020237,10020234,10020223,10020221,10020229,10020221,10020237,10020235,10020223,10020221,10020229,10020221,10020237,10020235,10020223,10020221,10020229,10020221,10020237,10020239,10020223,10020222,10020236,10020222,10020237,10020239,10020223,10020222,10020236,10020222,10020238,10020223,10020222,10020236,10020222,10020238,10020223,10020222,10020236,10020222,10020238,10020224,10020233,10020238,10020224,10020233,10020238,10020224,10020233,10020238,10020224,10020233,10020238,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020224,10020233,10020233,10020233,10020233,10020233,10020233,10020233</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L25 W17/25; N=151; EHP=11614.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x8,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L25 W17/25; N=151; EHP=31894.786320; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10020243,10020254,10020245,10048959,10020253,10020246,10020243,10020254,10020245,10048959,10020253,10020246,10020243,10020254,10020245,10048959,10020253,10020247,10020243,10020254,10020245,10048959,10020253,10020247,10020243,10020254,10020245,10020240,10020253,10020250,10020243,10020254,10020248,10020240,10020253,10020250,10020243,10020254,10020248,10020240,10020253,10020251,10020243,10020254,10020248,10020240,10020257,10020251,10020243,10020254,10020248,10048960,10020257,10020252,10020243,10020254,10020249,10048960,10020257,10020252,10020243,10020254,10020249,10048960,10020257,10045281,10020243,10020254,10020249,10048960,10020257,10020255,10020243,10020254,10020249,10020241,10020257,10020255,10020243,10020254,10020249,10020241,10020257,10020259,10020243,10020254,10020256,10020241,10020257,10020259,10020243,10020254,10020256,10020241,10020258,10020243,10020254,10020256,10020242,10020258,10020243,10020254,10020256,10020242,10020258,10020243,10020254,10020242,10020258,10020243,10020254,10020258,10020244,10020254,10020258,10020244,10020254,10020258,10020244,10020254,10020258,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020254,10020254,10020254,10020254</t>
+          <t>10020243,10048959,10020245,10048959,10020253,10020246,10020243,10048959,10020245,10048959,10020253,10020246,10020243,10048959,10020245,10048959,10020253,10020247,10020243,10048959,10020245,10048959,10020253,10020247,10020243,10020240,10020245,10020240,10020253,10020250,10020243,10020240,10020248,10020240,10020253,10020250,10020243,10020240,10020248,10020240,10020253,10020251,10020243,10020240,10020248,10020240,10020257,10020251,10020243,10048960,10020248,10048960,10020257,10020252,10020243,10048960,10020249,10048960,10020257,10020252,10020243,10048960,10020249,10048960,10020257,10045281,10020243,10048960,10020249,10048960,10020257,10020255,10020243,10020241,10020249,10020241,10020257,10020255,10020243,10020241,10020249,10020241,10020257,10020259,10020243,10020241,10020256,10020241,10020257,10020259,10020243,10020241,10020256,10020241,10020258,10020243,10020242,10020256,10020242,10020258,10020243,10020242,10020256,10020242,10020258,10020243,10020242,10020242,10020258,10020243,10020254,10020258,10020244,10020254,10020258,10020244,10020254,10020258,10020244,10020254,10020258,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020244,10020254,10020254,10020254,10020254,10020254</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L25 W18/25; N=157; EHP=12407.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x3,normal:17x20,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x43,heavy:86x1,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L25 W18/25; N=157; EHP=34079.488542; air:2x8,air:11x8,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x8,normal:17x20,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10020263,10020273,10020265,10048961,10020272,10045282,10020263,10020273,10020265,10048961,10020272,10045282,10020263,10020273,10020265,10048961,10020272,10020266,10020263,10020273,10020265,10048961,10020272,10020266,10020263,10020273,10020265,10020260,10020272,10020269,10020263,10020273,10020267,10020260,10020272,10020269,10020263,10020273,10020267,10020260,10020272,10020270,10020263,10020273,10020267,10020260,10020272,10020270,10020263,10020273,10020267,10048962,10020277,10020271,10020263,10020273,10020267,10048962,10020277,10020271,10020263,10020273,10020268,10048962,10020277,10020274,10020263,10020273,10020268,10048962,10020277,10020274,10020263,10020273,10020268,10020261,10020277,10020275,10020263,10020273,10020268,10020261,10020277,10020275,10020263,10020273,10020276,10020261,10020277,10020279,10020263,10020273,10020276,10020261,10020277,10020279,10020263,10020273,10020276,10020262,10020278,10020263,10020273,10020276,10020262,10020278,10020263,10020273,10020276,10020262,10020278,10020264,10020273,10020262,10020278,10020264,10020273,10020278,10020264,10020273,10020278,10020264,10020273,10020278,10020264,10020273,10020278,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020273,10020273,10020273,10020273,10020273,10020273</t>
+          <t>10020263,10048961,10020265,10048961,10020272,10045282,10020263,10048961,10020265,10048961,10020272,10045282,10020263,10048961,10020265,10048961,10020272,10020266,10020263,10048961,10020265,10048961,10020272,10020266,10020263,10020260,10020265,10020260,10020272,10020269,10020263,10020260,10020267,10020260,10020272,10020269,10020263,10020260,10020267,10020260,10020272,10020270,10020263,10020260,10020267,10020260,10020272,10020270,10020263,10048962,10020267,10048962,10020277,10020271,10020263,10048962,10020267,10048962,10020277,10020271,10020263,10048962,10020268,10048962,10020277,10020274,10020263,10048962,10020268,10048962,10020277,10020274,10020263,10020261,10020268,10020261,10020277,10020275,10020263,10020261,10020268,10020261,10020277,10020275,10020263,10020261,10020276,10020261,10020277,10020279,10020263,10020261,10020276,10020261,10020277,10020279,10020263,10020262,10020276,10020262,10020278,10020263,10020262,10020276,10020262,10020278,10020263,10020262,10020276,10020262,10020278,10020264,10020262,10020262,10020278,10020264,10020273,10020278,10020264,10020273,10020278,10020264,10020273,10020278,10020264,10020273,10020278,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020264,10020273,10020273,10020273,10020273,10020273,10020273,10020273</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L25 W19/25; N=163; EHP=14371.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L25 W19/25; N=163; EHP=39479.765467; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10020283,10020295,10020285,10048963,10020294,10020286,10020290,10020283,10020295,10020285,10048963,10020294,10020286,10020283,10020295,10020285,10048963,10020294,10020287,10020283,10020295,10020285,10048963,10020294,10020287,10020283,10020295,10020285,10020280,10020294,10020291,10020283,10020295,10020288,10020280,10020294,10020291,10020283,10020295,10020288,10020280,10020294,10020292,10020283,10020295,10020288,10020280,10020294,10020292,10020283,10020295,10020288,10048964,10020294,10020293,10020283,10020295,10020288,10048964,10020299,10020293,10020283,10020295,10020289,10048964,10020299,10020296,10020283,10020295,10020289,10048964,10020299,10020296,10020283,10020295,10020289,10020281,10020299,10020297,10020283,10020295,10020289,10020281,10020299,10020297,10020283,10020295,10020289,10020281,10020299,10020301,10020283,10020295,10020298,10020281,10020299,10020301,10020283,10020295,10020298,10020282,10020299,10020283,10020295,10020298,10020282,10020300,10020283,10020295,10020298,10020282,10020300,10020283,10020295,10020298,10020282,10020300,10020284,10020295,10020300,10020284,10020295,10020300,10020284,10020295,10020300,10020284,10020295,10020300,10020284,10020295,10020300,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020295,10020295,10020295,10020295,10020295,10020295,10020295</t>
+          <t>10020283,10048963,10020285,10048963,10020294,10020286,10020290,10020283,10048963,10020285,10048963,10020294,10020286,10020283,10048963,10020285,10048963,10020294,10020287,10020283,10048963,10020285,10048963,10020294,10020287,10020283,10020280,10020285,10020280,10020294,10020291,10020283,10020280,10020288,10020280,10020294,10020291,10020283,10020280,10020288,10020280,10020294,10020292,10020283,10020280,10020288,10020280,10020294,10020292,10020283,10048964,10020288,10048964,10020294,10020293,10020283,10048964,10020288,10048964,10020299,10020293,10020283,10048964,10020289,10048964,10020299,10020296,10020283,10048964,10020289,10048964,10020299,10020296,10020283,10020281,10020289,10020281,10020299,10020297,10020283,10020281,10020289,10020281,10020299,10020297,10020283,10020281,10020289,10020281,10020299,10020301,10020283,10020281,10020298,10020281,10020299,10020301,10020283,10020282,10020298,10020282,10020299,10020283,10020282,10020298,10020282,10020300,10020283,10020282,10020298,10020282,10020300,10020283,10020282,10020298,10020282,10020300,10020284,10020295,10020300,10020284,10020295,10020300,10020284,10020295,10020300,10020284,10020295,10020300,10020284,10020295,10020300,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020284,10020295,10020295,10020295,10020295,10020295,10020295,10020295,10020295</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L25 W20/25; N=169; EHP=24121.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L25 W20/25; N=169; EHP=66223.125722; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10020305,10020316,10020307,10048965,10020315,10020308,10020305,10020316,10020307,10048965,10020315,10020308,10020305,10020316,10020307,10048965,10020315,10020309,10020305,10020316,10020307,10048965,10020315,10020309,10020305,10020316,10020307,10020302,10020315,10020312,10020305,10020316,10020310,10020302,10020315,10020312,10020305,10020316,10020310,10020302,10020315,10020313,10020305,10020316,10020310,10020302,10020315,10020313,10020305,10020316,10020310,10020302,10020320,10020313,10020305,10020316,10020310,10048966,10020320,10020314,10020305,10020316,10020310,10048966,10020320,10020314,10020305,10020316,10020311,10048966,10020320,10020317,10020305,10020316,10020311,10048966,10020320,10020317,10020305,10020316,10020311,10020303,10020320,10020318,10020305,10020316,10020311,10020303,10020320,10020318,10020305,10020316,10020311,10020303,10020320,10020322,10020305,10020316,10020319,10020303,10020320,10020322,10020305,10020316,10020319,10020304,10020321,10020305,10020316,10020319,10020304,10020321,10020305,10020316,10020319,10020304,10020321,10020306,10020316,10020319,10020304,10020321,10020306,10020316,10020321,10020306,10020316,10020321,10020306,10020316,10020321,10020306,10020316,10020321,10020306,10020316,10020321,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020316,10020316,10020316,10020316,10020316,10020316,10020316,10020316</t>
+          <t>10020305,10048965,10020307,10048965,10020315,10020308,10020305,10048965,10020307,10048965,10020315,10020308,10020305,10048965,10020307,10048965,10020315,10020309,10020305,10048965,10020307,10048965,10020315,10020309,10020305,10020302,10020307,10020302,10020315,10020312,10020305,10020302,10020310,10020302,10020315,10020312,10020305,10020302,10020310,10020302,10020315,10020313,10020305,10020302,10020310,10020302,10020315,10020313,10020305,10020302,10020310,10020302,10020320,10020313,10020305,10048966,10020310,10048966,10020320,10020314,10020305,10048966,10020310,10048966,10020320,10020314,10020305,10048966,10020311,10048966,10020320,10020317,10020305,10048966,10020311,10048966,10020320,10020317,10020305,10020303,10020311,10020303,10020320,10020318,10020305,10020303,10020311,10020303,10020320,10020318,10020305,10020303,10020311,10020303,10020320,10020322,10020305,10020303,10020319,10020303,10020320,10020322,10020305,10020304,10020319,10020304,10020321,10020305,10020304,10020319,10020304,10020321,10020305,10020304,10020319,10020304,10020321,10020306,10020304,10020319,10020304,10020321,10020306,10020316,10020321,10020306,10020316,10020321,10020306,10020316,10020321,10020306,10020316,10020321,10020306,10020316,10020321,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020306,10020316,10020316,10020316,10020316,10020316,10020316,10020316,10020316,10020316</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L25 W21/25; N=175; EHP=24604.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x8,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L25 W21/25; N=175; EHP=67574.850894; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x9,normal:17x20,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10020326,10020337,10020328,10048967,10020336,10020329,10020326,10020337,10020328,10048967,10020336,10020329,10020326,10020337,10020328,10048967,10020336,10020330,10020326,10020337,10020328,10048967,10020336,10020330,10020326,10020337,10020328,10020323,10020336,10020333,10020326,10020337,10020331,10020323,10020336,10020333,10020326,10020337,10020331,10020323,10020336,10020333,10020326,10020337,10020331,10020323,10020336,10020334,10020326,10020337,10020331,10048968,10020336,10020334,10020326,10020337,10020331,10048968,10020341,10020335,10020326,10020337,10020332,10048968,10020341,10020335,10020326,10020337,10020332,10048968,10020341,10020338,10020326,10020337,10020332,10048968,10020341,10020338,10020326,10020337,10020332,10020324,10020341,10020339,10020326,10020337,10020332,10020324,10020341,10020339,10020326,10020337,10020332,10020324,10020341,10020339,10020326,10020337,10020340,10020324,10020341,10020343,10020326,10020337,10020340,10020325,10020341,10020343,10020326,10020337,10020340,10020325,10020342,10020326,10020337,10020340,10020325,10020342,10020326,10020337,10020340,10020325,10020342,10020326,10020337,10020325,10020342,10020327,10020337,10020342,10020327,10020337,10020342,10020327,10020337,10020342,10020327,10020337,10020342,10020327,10020337,10020342,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020337,10020337,10020337,10020337,10020337,10020337,10020337</t>
+          <t>10020326,10048967,10020328,10048967,10020336,10020329,10020326,10048967,10020328,10048967,10020336,10020329,10020326,10048967,10020328,10048967,10020336,10020330,10020326,10048967,10020328,10048967,10020336,10020330,10020326,10020323,10020328,10020323,10020336,10020333,10020326,10020323,10020331,10020323,10020336,10020333,10020326,10020323,10020331,10020323,10020336,10020333,10020326,10020323,10020331,10020323,10020336,10020334,10020326,10048968,10020331,10048968,10020336,10020334,10020326,10048968,10020331,10048968,10020341,10020335,10020326,10048968,10020332,10048968,10020341,10020335,10020326,10048968,10020332,10048968,10020341,10020338,10020326,10048968,10020332,10048968,10020341,10020338,10020326,10020324,10020332,10020324,10020341,10020339,10020326,10020324,10020332,10020324,10020341,10020339,10020326,10020324,10020332,10020324,10020341,10020339,10020326,10020324,10020340,10020324,10020341,10020343,10020326,10020325,10020340,10020325,10020341,10020343,10020326,10020325,10020340,10020325,10020342,10020326,10020325,10020340,10020325,10020342,10020326,10020325,10020340,10020325,10020342,10020326,10020325,10020325,10020342,10020327,10020337,10020342,10020327,10020337,10020342,10020327,10020337,10020342,10020327,10020337,10020342,10020327,10020337,10020342,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020327,10020337,10020337,10020337,10020337,10020337,10020337,10020337,10020337</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L25 W22/25; N=181; EHP=25097.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x5,normal:17x22,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L25 W22/25; N=181; EHP=68935.777175; air:2x8,air:11x8,air:12x10,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10020347,10020358,10020349,10048969,10020357,10020350,10020347,10020358,10020349,10048969,10020357,10020350,10020347,10020358,10020349,10048969,10020357,10020351,10020347,10020358,10020349,10048969,10020357,10020351,10020347,10020358,10020349,10048969,10020357,10020354,10020347,10020358,10020349,10020344,10020357,10020354,10020347,10020358,10020352,10020344,10020357,10020355,10020347,10020358,10020352,10020344,10020357,10020355,10020347,10020358,10020352,10020344,10020357,10020356,10020347,10020358,10020352,10048970,10020357,10020356,10020347,10020358,10020352,10048970,10020362,10020356,10020347,10020358,10020353,10048970,10020362,10020359,10020347,10020358,10020353,10048970,10020362,10020359,10020347,10020358,10020353,10048970,10020362,10020360,10020347,10020358,10020353,10020345,10020362,10020360,10020347,10020358,10020353,10020345,10020362,10020360,10020347,10020358,10020361,10020345,10020362,10020364,10020347,10020358,10020361,10020345,10020362,10020364,10020347,10020358,10020361,10020346,10020362,10020347,10020358,10020361,10020346,10020363,10020347,10020358,10020361,10020346,10020363,10020347,10020358,10020361,10020346,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020358,10020358,10020358,10020358,10020358,10020358,10020358</t>
+          <t>10020347,10048969,10020349,10048969,10020357,10020350,10020347,10048969,10020349,10048969,10020357,10020350,10020347,10048969,10020349,10048969,10020357,10020351,10020347,10048969,10020349,10048969,10020357,10020351,10020347,10048969,10020349,10048969,10020357,10020354,10020347,10020344,10020349,10020344,10020357,10020354,10020347,10020344,10020352,10020344,10020357,10020355,10020347,10020344,10020352,10020344,10020357,10020355,10020347,10020344,10020352,10020344,10020357,10020356,10020347,10048970,10020352,10048970,10020357,10020356,10020347,10048970,10020352,10048970,10020362,10020356,10020347,10048970,10020353,10048970,10020362,10020359,10020347,10048970,10020353,10048970,10020362,10020359,10020347,10048970,10020353,10048970,10020362,10020360,10020347,10020345,10020353,10020345,10020362,10020360,10020347,10020345,10020353,10020345,10020362,10020360,10020347,10020345,10020361,10020345,10020362,10020364,10020347,10020345,10020361,10020345,10020362,10020364,10020347,10020346,10020361,10020346,10020362,10020347,10020346,10020361,10020346,10020363,10020347,10020346,10020361,10020346,10020363,10020347,10020346,10020361,10020346,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020363,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020348,10020358,10020358,10020358,10020358,10020358,10020358,10020358,10020358</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L25 W23/25; N=187; EHP=25599.000000; air:2x5,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x22,normal:18x23,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x10,swarm:84x52,heavy:86x2,heavy:88x3,fast:98x6,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L25 W23/25; N=187; EHP=70290.303995; air:2x10,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x10,medium:108x9,medium:123x9,normal:17x22,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10020368,10020379,10020370,10048971,10020378,10020371,10020368,10020379,10020370,10048971,10020378,10020371,10020368,10020379,10020370,10048971,10020378,10020371,10020368,10020379,10020370,10048971,10020378,10020372,10020368,10020379,10020370,10048971,10020378,10020372,10020368,10020379,10020373,10020365,10020378,10020375,10020368,10020379,10020373,10020365,10020378,10020375,10020368,10020379,10020373,10020365,10020378,10020376,10020368,10020379,10020373,10020365,10020378,10020376,10020368,10020379,10020373,10020365,10020383,10020377,10020368,10020379,10020373,10048972,10020383,10020377,10020368,10020379,10020374,10048972,10020383,10020377,10020368,10020379,10020374,10048972,10020383,10020380,10020368,10020379,10020374,10048972,10020383,10020380,10020368,10020379,10020374,10020366,10020383,10020380,10020368,10020379,10020374,10020366,10020383,10020381,10020368,10020379,10020374,10020366,10020383,10020381,10020368,10020379,10020382,10020366,10020383,10020385,10020368,10020379,10020382,10020366,10020384,10020385,10020368,10020379,10020382,10020367,10020384,10020368,10020379,10020382,10020367,10020384,10020368,10020379,10020382,10020367,10020384,10020368,10020379,10020382,10020367,10020384,10020369,10020379,10020384,10020369,10020379,10020384,10020369,10020379,10020384,10020369,10020379,10020384,10020369,10020379,10020384,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020379,10020379,10020379,10020379,10020379,10020379,10020379,10020379</t>
+          <t>10020368,10048971,10020370,10048971,10020378,10020371,10020368,10048971,10020370,10048971,10020378,10020371,10020368,10048971,10020370,10048971,10020378,10020371,10020368,10048971,10020370,10048971,10020378,10020372,10020368,10048971,10020370,10048971,10020378,10020372,10020368,10020365,10020373,10020365,10020378,10020375,10020368,10020365,10020373,10020365,10020378,10020375,10020368,10020365,10020373,10020365,10020378,10020376,10020368,10020365,10020373,10020365,10020378,10020376,10020368,10020365,10020373,10020365,10020383,10020377,10020368,10048972,10020373,10048972,10020383,10020377,10020368,10048972,10020374,10048972,10020383,10020377,10020368,10048972,10020374,10048972,10020383,10020380,10020368,10048972,10020374,10048972,10020383,10020380,10020368,10020366,10020374,10020366,10020383,10020380,10020368,10020366,10020374,10020366,10020383,10020381,10020368,10020366,10020374,10020366,10020383,10020381,10020368,10020366,10020382,10020366,10020383,10020385,10020368,10020366,10020382,10020366,10020384,10020385,10020368,10020367,10020382,10020367,10020384,10020368,10020367,10020382,10020367,10020384,10020368,10020367,10020382,10020367,10020384,10020368,10020367,10020382,10020367,10020384,10020369,10020379,10020384,10020369,10020379,10020384,10020369,10020379,10020384,10020369,10020379,10020384,10020369,10020379,10020384,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020369,10020379,10020379,10020379,10020379,10020379,10020379,10020379,10020379,10020379</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L25 W24/25; N=193; EHP=27412.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x23,normal:18x23,fast:30x5,heavy:31x3,heavy:40x2,fast:58x6,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x54,heavy:86x3,heavy:88x2,fast:98x6,medium:108x9,medium:123x10,heavy:127x2</t>
+          <t>L25 W24/25; N=193; EHP=75281.266646; air:2x10,air:11x10,air:12x8,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x6,fast:98x6,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x10,normal:17x23,normal:18x23,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10020389,10020400,10020391,10048973,10020399,10020392,10020407,10020389,10020400,10020391,10048973,10020399,10020392,10020389,10020400,10020391,10048973,10020399,10020392,10020389,10020400,10020391,10048973,10020399,10020393,10020389,10020400,10020391,10020386,10020399,10020393,10020389,10020400,10020391,10020386,10020399,10020393,10020389,10020400,10020394,10020386,10020399,10020396,10020389,10020400,10020394,10020386,10020399,10020396,10020389,10020400,10020394,10020386,10020399,10020397,10020389,10020400,10020394,10048974,10020399,10020397,10020389,10020400,10020394,10048974,10020404,10020398,10020389,10020400,10020394,10048974,10020404,10020398,10020389,10020400,10020395,10048974,10020404,10020401,10020389,10020400,10020395,10048974,10020404,10020401,10020389,10020400,10020395,10020387,10020404,10020401,10020389,10020400,10020395,10020387,10020404,10020402,10020389,10020400,10020395,10020387,10020404,10020402,10020389,10020400,10020395,10020387,10020404,10020406,10020389,10020400,10020403,10020387,10020404,10020406,10020389,10020400,10020403,10020388,10020404,10020389,10020400,10020403,10020388,10020405,10020389,10020400,10020403,10020388,10020405,10020389,10020400,10020403,10020388,10020405,10020389,10020400,10020388,10020405,10020390,10020400,10020405,10020390,10020400,10020405,10020390,10020400,10020405,10020390,10020400,10020405,10020390,10020400,10020405,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020400,10020400,10020400,10020400,10020400,10020400,10020400</t>
+          <t>10020389,10048973,10020391,10048973,10020399,10020392,10020407,10020389,10048973,10020391,10048973,10020399,10020392,10020389,10048973,10020391,10048973,10020399,10020392,10020389,10048973,10020391,10048973,10020399,10020393,10020389,10020386,10020391,10020386,10020399,10020393,10020389,10020386,10020391,10020386,10020399,10020393,10020389,10020386,10020394,10020386,10020399,10020396,10020389,10020386,10020394,10020386,10020399,10020396,10020389,10020386,10020394,10020386,10020399,10020397,10020389,10048974,10020394,10048974,10020399,10020397,10020389,10048974,10020394,10048974,10020404,10020398,10020389,10048974,10020394,10048974,10020404,10020398,10020389,10048974,10020395,10048974,10020404,10020401,10020389,10048974,10020395,10048974,10020404,10020401,10020389,10020387,10020395,10020387,10020404,10020401,10020389,10020387,10020395,10020387,10020404,10020402,10020389,10020387,10020395,10020387,10020404,10020402,10020389,10020387,10020395,10020387,10020404,10020406,10020389,10020387,10020403,10020387,10020404,10020406,10020389,10020388,10020403,10020388,10020404,10020389,10020388,10020403,10020388,10020405,10020389,10020388,10020403,10020388,10020405,10020389,10020388,10020403,10020388,10020405,10020389,10020388,10020388,10020405,10020390,10020400,10020405,10020390,10020400,10020405,10020390,10020400,10020405,10020390,10020400,10020405,10020390,10020400,10020405,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020390,10020400,10020400,10020400,10020400,10020400,10020400,10020400,10020400</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L25 W25/25; N=199; EHP=54709.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x24,normal:18x24,fast:30x6,heavy:31x3,heavy:40x3,fast:58x6,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x10,swarm:84x55,heavy:86x3,heavy:88x2,fast:98x5,medium:108x10,medium:123x9,heavy:127x2,boss:132x1</t>
+          <t>L25 W25/25; N=199; EHP=150237.894353; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x10,medium:108x10,medium:123x9,normal:17x24,normal:18x24,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L25/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L25/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>232</v>
+        <v>360</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>225</v>
+        <v>320</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>218</v>
+        <v>290</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>211</v>
+        <v>370</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>197</v>
+        <v>290</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>190</v>
+        <v>370</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>176</v>
+        <v>310</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>169</v>
+        <v>290</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>162</v>
+        <v>370</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>155</v>
+        <v>300</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>148</v>
+        <v>280</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>134</v>
+        <v>310</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
